--- a/PROGRAMACION 12-04-2026.xlsx
+++ b/PROGRAMACION 12-04-2026.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prueba\ENVIO MASIVO DE MENSAJES 2026 MARZO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD4CCA1-954E-46C9-93EE-E6E0D244C4FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E618C25E-BD8F-4BA4-B760-377E3CE86128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{B72AB2B8-5376-4A67-BE8D-5E91B2913CFD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Coordinación" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$CH$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Coordinación!$A$1:$CH$20</definedName>
     <definedName name="BD_Causal_Cierre">OFFSET(#REF!,1,0,COUNTA(#REF!),1)</definedName>
     <definedName name="BD_Cod_Inspec">OFFSET(#REF!,1,0,COUNTA(#REF!),1)</definedName>
     <definedName name="BD_Jornada">OFFSET(#REF!,1,0,COUNTA(#REF!),1)</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="290">
   <si>
     <t>Orden</t>
   </si>
@@ -370,9 +370,6 @@
   </si>
   <si>
     <t>Cali</t>
-  </si>
-  <si>
-    <t>Hurtado Hinestroza Alex</t>
   </si>
   <si>
     <t>31251134</t>
@@ -2098,7 +2095,7 @@
         <v>96</v>
       </c>
       <c r="CB2" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CC2" s="37">
         <v>1</v>
@@ -2128,10 +2125,10 @@
         <v>100237</v>
       </c>
       <c r="F3" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="34" t="s">
         <v>110</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>111</v>
       </c>
       <c r="H3" s="34" t="s">
         <v>86</v>
@@ -2140,19 +2137,19 @@
         <v>87</v>
       </c>
       <c r="J3" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="K3" s="34" t="s">
+      <c r="L3" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="L3" s="34" t="s">
+      <c r="M3" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="N3" s="32" t="s">
         <v>115</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>116</v>
       </c>
       <c r="O3" s="32" t="s">
         <v>93</v>
@@ -2167,7 +2164,7 @@
         <v>46028</v>
       </c>
       <c r="S3" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T3" s="32">
         <v>437820845</v>
@@ -2179,7 +2176,7 @@
         <v>46119</v>
       </c>
       <c r="W3" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X3" s="36"/>
       <c r="Y3" s="32" t="s">
@@ -2207,7 +2204,7 @@
         <v>3163671442</v>
       </c>
       <c r="AG3" s="34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AH3" s="32" t="s">
         <v>98</v>
@@ -2290,10 +2287,10 @@
         <v>1</v>
       </c>
       <c r="BT3" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU3" s="32" t="s">
         <v>119</v>
-      </c>
-      <c r="BU3" s="32" t="s">
-        <v>120</v>
       </c>
       <c r="BV3" s="32" t="s">
         <v>105</v>
@@ -2314,7 +2311,7 @@
         <v>96</v>
       </c>
       <c r="CB3" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CC3" s="37">
         <v>1</v>
@@ -2326,7 +2323,7 @@
       <c r="CF3" s="34"/>
       <c r="CG3" s="32"/>
       <c r="CH3" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:86" x14ac:dyDescent="0.3">
@@ -2346,10 +2343,10 @@
         <v>100237</v>
       </c>
       <c r="F4" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="34" t="s">
         <v>122</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>123</v>
       </c>
       <c r="H4" s="34" t="s">
         <v>86</v>
@@ -2358,19 +2355,19 @@
         <v>87</v>
       </c>
       <c r="J4" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="L4" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="M4" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="N4" s="32" t="s">
         <v>127</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>128</v>
       </c>
       <c r="O4" s="32" t="s">
         <v>93</v>
@@ -2385,7 +2382,7 @@
         <v>46028</v>
       </c>
       <c r="S4" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T4" s="32">
         <v>437554045</v>
@@ -2397,7 +2394,7 @@
         <v>46114</v>
       </c>
       <c r="W4" s="33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="X4" s="36"/>
       <c r="Y4" s="32" t="s">
@@ -2419,13 +2416,13 @@
         <v>46124</v>
       </c>
       <c r="AE4" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF4" s="37">
         <v>3132093396</v>
       </c>
       <c r="AG4" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AH4" s="32" t="s">
         <v>98</v>
@@ -2508,7 +2505,7 @@
         <v>-4</v>
       </c>
       <c r="BT4" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BU4" s="32" t="s">
         <v>104</v>
@@ -2532,7 +2529,7 @@
         <v>96</v>
       </c>
       <c r="CB4" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CC4" s="37">
         <v>1</v>
@@ -2544,7 +2541,7 @@
       <c r="CF4" s="34"/>
       <c r="CG4" s="32"/>
       <c r="CH4" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:86" x14ac:dyDescent="0.3">
@@ -2564,10 +2561,10 @@
         <v>266</v>
       </c>
       <c r="F5" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="34" t="s">
         <v>132</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>133</v>
       </c>
       <c r="H5" s="34" t="s">
         <v>86</v>
@@ -2576,19 +2573,19 @@
         <v>87</v>
       </c>
       <c r="J5" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="K5" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="K5" s="34" t="s">
+      <c r="L5" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="M5" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="N5" s="32" t="s">
         <v>137</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>138</v>
       </c>
       <c r="O5" s="32" t="s">
         <v>93</v>
@@ -2603,7 +2600,7 @@
         <v>46081</v>
       </c>
       <c r="S5" s="33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T5" s="32">
         <v>433310914</v>
@@ -2615,7 +2612,7 @@
         <v>46081</v>
       </c>
       <c r="W5" s="33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X5" s="36"/>
       <c r="Y5" s="32" t="s">
@@ -2637,13 +2634,13 @@
         <v>46124</v>
       </c>
       <c r="AE5" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF5" s="37">
         <v>3005796351</v>
       </c>
       <c r="AG5" s="34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AH5" s="32" t="s">
         <v>98</v>
@@ -2726,7 +2723,7 @@
         <v>-34</v>
       </c>
       <c r="BT5" s="32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BU5" s="32" t="s">
         <v>104</v>
@@ -2747,10 +2744,10 @@
         <v>108</v>
       </c>
       <c r="CA5" s="34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="CB5" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="CC5" s="37">
         <v>1</v>
@@ -2780,10 +2777,10 @@
         <v>266</v>
       </c>
       <c r="F6" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="34" t="s">
         <v>141</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>142</v>
       </c>
       <c r="H6" s="34" t="s">
         <v>86</v>
@@ -2792,22 +2789,22 @@
         <v>87</v>
       </c>
       <c r="J6" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K6" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="L6" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="L6" s="34" t="s">
+      <c r="M6" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="N6" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="O6" s="32" t="s">
         <v>146</v>
-      </c>
-      <c r="O6" s="32" t="s">
-        <v>147</v>
       </c>
       <c r="P6" s="32">
         <v>4644</v>
@@ -2819,7 +2816,7 @@
         <v>46107</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="T6" s="32"/>
       <c r="U6" s="32"/>
@@ -2827,10 +2824,10 @@
       <c r="W6" s="33"/>
       <c r="X6" s="36"/>
       <c r="Y6" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z6" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA6" s="34" t="s">
         <v>96</v>
@@ -2851,13 +2848,13 @@
         <v>3183498170</v>
       </c>
       <c r="AG6" s="34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH6" s="32" t="s">
         <v>98</v>
       </c>
       <c r="AI6" s="32">
-        <v>373</v>
+        <v>12345</v>
       </c>
       <c r="AJ6" s="35">
         <v>46120</v>
@@ -2898,7 +2895,7 @@
         <v>46108</v>
       </c>
       <c r="BH6" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BI6" s="35" t="s">
         <v>96</v>
@@ -2934,7 +2931,7 @@
         <v>-12</v>
       </c>
       <c r="BT6" s="32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BU6" s="32" t="s">
         <v>104</v>
@@ -2943,7 +2940,7 @@
         <v>105</v>
       </c>
       <c r="BW6" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BX6" s="35">
         <v>40775</v>
@@ -2958,7 +2955,7 @@
         <v>96</v>
       </c>
       <c r="CB6" s="34" t="s">
-        <v>109</v>
+        <v>289</v>
       </c>
       <c r="CC6" s="37">
         <v>1</v>
@@ -2988,10 +2985,10 @@
         <v>100014</v>
       </c>
       <c r="F7" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>154</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>155</v>
       </c>
       <c r="H7" s="34" t="s">
         <v>86</v>
@@ -3000,19 +2997,19 @@
         <v>87</v>
       </c>
       <c r="J7" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="K7" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="K7" s="34" t="s">
+      <c r="L7" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="L7" s="34" t="s">
+      <c r="M7" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="N7" s="32" t="s">
         <v>159</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>160</v>
       </c>
       <c r="O7" s="32" t="s">
         <v>93</v>
@@ -3027,7 +3024,7 @@
         <v>46112</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T7" s="32">
         <v>436986458</v>
@@ -3039,7 +3036,7 @@
         <v>46112</v>
       </c>
       <c r="W7" s="33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="X7" s="36"/>
       <c r="Y7" s="32" t="s">
@@ -3067,13 +3064,13 @@
         <v>3186440791</v>
       </c>
       <c r="AG7" s="34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AH7" s="32" t="s">
         <v>98</v>
       </c>
       <c r="AI7" s="32">
-        <v>127</v>
+        <v>12345</v>
       </c>
       <c r="AJ7" s="35">
         <v>46120</v>
@@ -3135,10 +3132,10 @@
         <v>100</v>
       </c>
       <c r="BO7" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP7" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP7" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ7" s="37">
         <v>63</v>
@@ -3150,7 +3147,7 @@
         <v>-7</v>
       </c>
       <c r="BT7" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BU7" s="32" t="s">
         <v>104</v>
@@ -3159,7 +3156,7 @@
         <v>105</v>
       </c>
       <c r="BW7" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BX7" s="35">
         <v>44215</v>
@@ -3174,7 +3171,7 @@
         <v>96</v>
       </c>
       <c r="CB7" s="34" t="s">
-        <v>165</v>
+        <v>289</v>
       </c>
       <c r="CC7" s="37">
         <v>1</v>
@@ -3204,10 +3201,10 @@
         <v>100014</v>
       </c>
       <c r="F8" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="G8" s="34" t="s">
         <v>166</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>167</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>86</v>
@@ -3216,19 +3213,19 @@
         <v>87</v>
       </c>
       <c r="J8" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="K8" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="L8" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="L8" s="34" t="s">
+      <c r="M8" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="M8" s="32" t="s">
+      <c r="N8" s="32" t="s">
         <v>171</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>172</v>
       </c>
       <c r="O8" s="32" t="s">
         <v>93</v>
@@ -3243,7 +3240,7 @@
         <v>46119</v>
       </c>
       <c r="S8" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="T8" s="32"/>
       <c r="U8" s="32"/>
@@ -3251,19 +3248,19 @@
       <c r="W8" s="33"/>
       <c r="X8" s="36"/>
       <c r="Y8" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z8" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA8" s="34" t="s">
         <v>174</v>
-      </c>
-      <c r="AA8" s="34" t="s">
-        <v>175</v>
       </c>
       <c r="AB8" s="35">
         <v>46081</v>
       </c>
       <c r="AC8" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD8" s="35">
         <v>46121</v>
@@ -3275,7 +3272,7 @@
         <v>3206094305</v>
       </c>
       <c r="AG8" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AH8" s="32" t="s">
         <v>98</v>
@@ -3322,7 +3319,7 @@
         <v>46120</v>
       </c>
       <c r="BH8" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BI8" s="35" t="s">
         <v>96</v>
@@ -3343,10 +3340,10 @@
         <v>100</v>
       </c>
       <c r="BO8" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP8" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP8" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ8" s="37">
         <v>60</v>
@@ -3358,16 +3355,16 @@
         <v>0</v>
       </c>
       <c r="BT8" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BU8" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BV8" s="32" t="s">
         <v>105</v>
       </c>
       <c r="BW8" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BX8" s="35">
         <v>44292</v>
@@ -3382,7 +3379,7 @@
         <v>96</v>
       </c>
       <c r="CB8" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="CC8" s="37">
         <v>1</v>
@@ -3394,7 +3391,7 @@
       <c r="CF8" s="34"/>
       <c r="CG8" s="32"/>
       <c r="CH8" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:86" x14ac:dyDescent="0.3">
@@ -3414,10 +3411,10 @@
         <v>100014</v>
       </c>
       <c r="F9" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="34" t="s">
         <v>180</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>181</v>
       </c>
       <c r="H9" s="34" t="s">
         <v>86</v>
@@ -3426,19 +3423,19 @@
         <v>87</v>
       </c>
       <c r="J9" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="K9" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="K9" s="34" t="s">
+      <c r="L9" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="M9" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="N9" s="32" t="s">
         <v>185</v>
-      </c>
-      <c r="N9" s="32" t="s">
-        <v>186</v>
       </c>
       <c r="O9" s="32" t="s">
         <v>93</v>
@@ -3453,7 +3450,7 @@
         <v>46113</v>
       </c>
       <c r="S9" s="33" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="T9" s="32">
         <v>437299053</v>
@@ -3465,7 +3462,7 @@
         <v>46113</v>
       </c>
       <c r="W9" s="33" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X9" s="36"/>
       <c r="Y9" s="32" t="s">
@@ -3493,7 +3490,7 @@
         <v>3177590235</v>
       </c>
       <c r="AG9" s="34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AH9" s="32" t="s">
         <v>98</v>
@@ -3561,10 +3558,10 @@
         <v>100</v>
       </c>
       <c r="BO9" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP9" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP9" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ9" s="37">
         <v>62</v>
@@ -3576,7 +3573,7 @@
         <v>-6</v>
       </c>
       <c r="BT9" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BU9" s="32" t="s">
         <v>104</v>
@@ -3585,7 +3582,7 @@
         <v>105</v>
       </c>
       <c r="BW9" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BX9" s="35">
         <v>44231</v>
@@ -3600,7 +3597,7 @@
         <v>96</v>
       </c>
       <c r="CB9" s="34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="CC9" s="37">
         <v>1</v>
@@ -3630,10 +3627,10 @@
         <v>100014</v>
       </c>
       <c r="F10" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="34" t="s">
         <v>189</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>190</v>
       </c>
       <c r="H10" s="34" t="s">
         <v>86</v>
@@ -3642,19 +3639,19 @@
         <v>87</v>
       </c>
       <c r="J10" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="K10" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="L10" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="M10" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="N10" s="32" t="s">
         <v>194</v>
-      </c>
-      <c r="N10" s="32" t="s">
-        <v>195</v>
       </c>
       <c r="O10" s="32" t="s">
         <v>93</v>
@@ -3669,7 +3666,7 @@
         <v>46093</v>
       </c>
       <c r="S10" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="T10" s="32">
         <v>435120910</v>
@@ -3681,7 +3678,7 @@
         <v>46093</v>
       </c>
       <c r="W10" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X10" s="36"/>
       <c r="Y10" s="32" t="s">
@@ -3703,11 +3700,11 @@
         <v>46121</v>
       </c>
       <c r="AE10" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF10" s="37"/>
       <c r="AG10" s="34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH10" s="32" t="s">
         <v>98</v>
@@ -3775,10 +3772,10 @@
         <v>100</v>
       </c>
       <c r="BO10" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP10" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP10" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ10" s="37">
         <v>69</v>
@@ -3790,7 +3787,7 @@
         <v>-26</v>
       </c>
       <c r="BT10" s="32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BU10" s="32" t="s">
         <v>104</v>
@@ -3799,7 +3796,7 @@
         <v>105</v>
       </c>
       <c r="BW10" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BX10" s="35">
         <v>44019</v>
@@ -3814,7 +3811,7 @@
         <v>96</v>
       </c>
       <c r="CB10" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="CC10" s="37">
         <v>1</v>
@@ -3844,10 +3841,10 @@
         <v>266</v>
       </c>
       <c r="F11" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G11" s="34" t="s">
         <v>199</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>200</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>86</v>
@@ -3856,19 +3853,19 @@
         <v>87</v>
       </c>
       <c r="J11" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="K11" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="K11" s="34" t="s">
+      <c r="L11" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="L11" s="34" t="s">
+      <c r="M11" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="M11" s="32" t="s">
+      <c r="N11" s="32" t="s">
         <v>204</v>
-      </c>
-      <c r="N11" s="32" t="s">
-        <v>205</v>
       </c>
       <c r="O11" s="32" t="s">
         <v>93</v>
@@ -3883,7 +3880,7 @@
         <v>46112</v>
       </c>
       <c r="S11" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T11" s="32">
         <v>436980079</v>
@@ -3895,7 +3892,7 @@
         <v>46112</v>
       </c>
       <c r="W11" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X11" s="36"/>
       <c r="Y11" s="32" t="s">
@@ -3923,7 +3920,7 @@
         <v>3176386989</v>
       </c>
       <c r="AG11" s="34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AH11" s="32" t="s">
         <v>98</v>
@@ -3991,10 +3988,10 @@
         <v>100</v>
       </c>
       <c r="BO11" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP11" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP11" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ11" s="37">
         <v>60</v>
@@ -4006,7 +4003,7 @@
         <v>-6</v>
       </c>
       <c r="BT11" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BU11" s="32" t="s">
         <v>104</v>
@@ -4030,7 +4027,7 @@
         <v>96</v>
       </c>
       <c r="CB11" s="34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="CC11" s="37">
         <v>1</v>
@@ -4042,7 +4039,7 @@
       <c r="CF11" s="34"/>
       <c r="CG11" s="32"/>
       <c r="CH11" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:86" x14ac:dyDescent="0.3">
@@ -4062,10 +4059,10 @@
         <v>266</v>
       </c>
       <c r="F12" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="G12" s="34" t="s">
         <v>208</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>209</v>
       </c>
       <c r="H12" s="34" t="s">
         <v>86</v>
@@ -4074,19 +4071,19 @@
         <v>87</v>
       </c>
       <c r="J12" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="K12" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="K12" s="34" t="s">
+      <c r="L12" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="M12" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="M12" s="32" t="s">
+      <c r="N12" s="32" t="s">
         <v>213</v>
-      </c>
-      <c r="N12" s="32" t="s">
-        <v>214</v>
       </c>
       <c r="O12" s="32" t="s">
         <v>93</v>
@@ -4101,7 +4098,7 @@
         <v>46108</v>
       </c>
       <c r="S12" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T12" s="32">
         <v>436621903</v>
@@ -4113,7 +4110,7 @@
         <v>46108</v>
       </c>
       <c r="W12" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X12" s="36"/>
       <c r="Y12" s="32" t="s">
@@ -4141,7 +4138,7 @@
         <v>3157712504</v>
       </c>
       <c r="AG12" s="34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH12" s="32" t="s">
         <v>98</v>
@@ -4209,10 +4206,10 @@
         <v>100</v>
       </c>
       <c r="BO12" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP12" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP12" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ12" s="37">
         <v>60</v>
@@ -4224,7 +4221,7 @@
         <v>-10</v>
       </c>
       <c r="BT12" s="32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BU12" s="32" t="s">
         <v>104</v>
@@ -4248,7 +4245,7 @@
         <v>96</v>
       </c>
       <c r="CB12" s="34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="CC12" s="37">
         <v>1</v>
@@ -4260,7 +4257,7 @@
       <c r="CF12" s="34"/>
       <c r="CG12" s="32"/>
       <c r="CH12" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:86" x14ac:dyDescent="0.3">
@@ -4280,10 +4277,10 @@
         <v>266</v>
       </c>
       <c r="F13" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="34" t="s">
         <v>218</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>219</v>
       </c>
       <c r="H13" s="34" t="s">
         <v>86</v>
@@ -4292,19 +4289,19 @@
         <v>87</v>
       </c>
       <c r="J13" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="K13" s="34" t="s">
+      <c r="L13" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="L13" s="34" t="s">
+      <c r="M13" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="N13" s="32" t="s">
         <v>223</v>
-      </c>
-      <c r="N13" s="32" t="s">
-        <v>224</v>
       </c>
       <c r="O13" s="32" t="s">
         <v>93</v>
@@ -4319,7 +4316,7 @@
         <v>46119</v>
       </c>
       <c r="S13" s="33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T13" s="32">
         <v>437869392</v>
@@ -4331,7 +4328,7 @@
         <v>46119</v>
       </c>
       <c r="W13" s="33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X13" s="36"/>
       <c r="Y13" s="32" t="s">
@@ -4353,13 +4350,13 @@
         <v>46121</v>
       </c>
       <c r="AE13" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF13" s="37">
         <v>3127050690</v>
       </c>
       <c r="AG13" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AH13" s="32" t="s">
         <v>98</v>
@@ -4427,10 +4424,10 @@
         <v>100</v>
       </c>
       <c r="BO13" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP13" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP13" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ13" s="37">
         <v>56</v>
@@ -4442,10 +4439,10 @@
         <v>4</v>
       </c>
       <c r="BT13" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BU13" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BV13" s="32" t="s">
         <v>105</v>
@@ -4466,7 +4463,7 @@
         <v>96</v>
       </c>
       <c r="CB13" s="34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="CC13" s="37">
         <v>1</v>
@@ -4496,10 +4493,10 @@
         <v>266</v>
       </c>
       <c r="F14" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="G14" s="34" t="s">
         <v>228</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>229</v>
       </c>
       <c r="H14" s="34" t="s">
         <v>86</v>
@@ -4508,19 +4505,19 @@
         <v>87</v>
       </c>
       <c r="J14" s="34" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K14" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="L14" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="L14" s="34" t="s">
+      <c r="M14" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="M14" s="32" t="s">
+      <c r="N14" s="32" t="s">
         <v>232</v>
-      </c>
-      <c r="N14" s="32" t="s">
-        <v>233</v>
       </c>
       <c r="O14" s="32" t="s">
         <v>93</v>
@@ -4535,7 +4532,7 @@
         <v>46119</v>
       </c>
       <c r="S14" s="33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T14" s="32">
         <v>437868284</v>
@@ -4547,7 +4544,7 @@
         <v>46119</v>
       </c>
       <c r="W14" s="33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="X14" s="36"/>
       <c r="Y14" s="32" t="s">
@@ -4569,13 +4566,13 @@
         <v>46121</v>
       </c>
       <c r="AE14" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF14" s="37">
         <v>3128094999</v>
       </c>
       <c r="AG14" s="34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AH14" s="32" t="s">
         <v>98</v>
@@ -4643,10 +4640,10 @@
         <v>100</v>
       </c>
       <c r="BO14" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP14" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP14" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ14" s="37">
         <v>56</v>
@@ -4658,10 +4655,10 @@
         <v>4</v>
       </c>
       <c r="BT14" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BU14" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BV14" s="32" t="s">
         <v>105</v>
@@ -4682,7 +4679,7 @@
         <v>96</v>
       </c>
       <c r="CB14" s="34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="CC14" s="37">
         <v>1</v>
@@ -4712,10 +4709,10 @@
         <v>100237</v>
       </c>
       <c r="F15" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="G15" s="34" t="s">
         <v>235</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>236</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>86</v>
@@ -4724,19 +4721,19 @@
         <v>87</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K15" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="L15" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="L15" s="34" t="s">
+      <c r="M15" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="M15" s="32" t="s">
+      <c r="N15" s="32" t="s">
         <v>239</v>
-      </c>
-      <c r="N15" s="32" t="s">
-        <v>240</v>
       </c>
       <c r="O15" s="32" t="s">
         <v>93</v>
@@ -4751,7 +4748,7 @@
         <v>46027</v>
       </c>
       <c r="S15" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T15" s="32">
         <v>437589114</v>
@@ -4763,7 +4760,7 @@
         <v>46116</v>
       </c>
       <c r="W15" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="X15" s="36"/>
       <c r="Y15" s="32" t="s">
@@ -4791,7 +4788,7 @@
         <v>3165576185</v>
       </c>
       <c r="AG15" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AH15" s="32" t="s">
         <v>98</v>
@@ -4859,10 +4856,10 @@
         <v>100</v>
       </c>
       <c r="BO15" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP15" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP15" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ15" s="37">
         <v>60</v>
@@ -4898,7 +4895,7 @@
         <v>96</v>
       </c>
       <c r="CB15" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CC15" s="37">
         <v>1</v>
@@ -4910,7 +4907,7 @@
       <c r="CF15" s="34"/>
       <c r="CG15" s="32"/>
       <c r="CH15" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:86" x14ac:dyDescent="0.3">
@@ -4930,10 +4927,10 @@
         <v>266</v>
       </c>
       <c r="F16" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="G16" s="34" t="s">
         <v>243</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>244</v>
       </c>
       <c r="H16" s="34" t="s">
         <v>86</v>
@@ -4942,19 +4939,19 @@
         <v>87</v>
       </c>
       <c r="J16" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="K16" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="K16" s="34" t="s">
+      <c r="L16" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="L16" s="34" t="s">
+      <c r="M16" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="N16" s="32" t="s">
         <v>248</v>
-      </c>
-      <c r="N16" s="32" t="s">
-        <v>249</v>
       </c>
       <c r="O16" s="32" t="s">
         <v>93</v>
@@ -4969,7 +4966,7 @@
         <v>46119</v>
       </c>
       <c r="S16" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T16" s="32">
         <v>437822236</v>
@@ -4981,7 +4978,7 @@
         <v>46119</v>
       </c>
       <c r="W16" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="X16" s="36"/>
       <c r="Y16" s="32" t="s">
@@ -5009,7 +5006,7 @@
         <v>3105069815</v>
       </c>
       <c r="AG16" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AH16" s="32" t="s">
         <v>98</v>
@@ -5077,10 +5074,10 @@
         <v>100</v>
       </c>
       <c r="BO16" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP16" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP16" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ16" s="37">
         <v>42</v>
@@ -5092,10 +5089,10 @@
         <v>4</v>
       </c>
       <c r="BT16" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BU16" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BV16" s="32" t="s">
         <v>105</v>
@@ -5116,7 +5113,7 @@
         <v>96</v>
       </c>
       <c r="CB16" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="CC16" s="37">
         <v>1</v>
@@ -5146,10 +5143,10 @@
         <v>100237</v>
       </c>
       <c r="F17" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="G17" s="34" t="s">
         <v>251</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>252</v>
       </c>
       <c r="H17" s="34" t="s">
         <v>86</v>
@@ -5158,19 +5155,19 @@
         <v>87</v>
       </c>
       <c r="J17" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="K17" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="K17" s="34" t="s">
+      <c r="L17" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="L17" s="34" t="s">
+      <c r="M17" s="32" t="s">
         <v>255</v>
       </c>
-      <c r="M17" s="32" t="s">
+      <c r="N17" s="32" t="s">
         <v>256</v>
-      </c>
-      <c r="N17" s="32" t="s">
-        <v>257</v>
       </c>
       <c r="O17" s="32" t="s">
         <v>93</v>
@@ -5185,7 +5182,7 @@
         <v>46027</v>
       </c>
       <c r="S17" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T17" s="32">
         <v>437555468</v>
@@ -5197,7 +5194,7 @@
         <v>46114</v>
       </c>
       <c r="W17" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="X17" s="36"/>
       <c r="Y17" s="32" t="s">
@@ -5225,7 +5222,7 @@
         <v>3127585257</v>
       </c>
       <c r="AG17" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AH17" s="32" t="s">
         <v>98</v>
@@ -5293,10 +5290,10 @@
         <v>100</v>
       </c>
       <c r="BO17" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP17" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP17" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ17" s="37">
         <v>60</v>
@@ -5308,7 +5305,7 @@
         <v>-4</v>
       </c>
       <c r="BT17" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BU17" s="32" t="s">
         <v>104</v>
@@ -5332,7 +5329,7 @@
         <v>96</v>
       </c>
       <c r="CB17" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CC17" s="37">
         <v>1</v>
@@ -5344,7 +5341,7 @@
       <c r="CF17" s="34"/>
       <c r="CG17" s="32"/>
       <c r="CH17" s="34" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:86" x14ac:dyDescent="0.3">
@@ -5364,10 +5361,10 @@
         <v>100237</v>
       </c>
       <c r="F18" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="G18" s="34" t="s">
         <v>259</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>260</v>
       </c>
       <c r="H18" s="34" t="s">
         <v>86</v>
@@ -5376,19 +5373,19 @@
         <v>87</v>
       </c>
       <c r="J18" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="K18" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="K18" s="34" t="s">
+      <c r="L18" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="L18" s="34" t="s">
+      <c r="M18" s="32" t="s">
         <v>263</v>
       </c>
-      <c r="M18" s="32" t="s">
+      <c r="N18" s="32" t="s">
         <v>264</v>
-      </c>
-      <c r="N18" s="32" t="s">
-        <v>265</v>
       </c>
       <c r="O18" s="32" t="s">
         <v>93</v>
@@ -5403,7 +5400,7 @@
         <v>46028</v>
       </c>
       <c r="S18" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T18" s="32">
         <v>437657507</v>
@@ -5415,7 +5412,7 @@
         <v>46118</v>
       </c>
       <c r="W18" s="33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="X18" s="36"/>
       <c r="Y18" s="32" t="s">
@@ -5443,7 +5440,7 @@
         <v>3154769175</v>
       </c>
       <c r="AG18" s="34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AH18" s="32" t="s">
         <v>98</v>
@@ -5511,10 +5508,10 @@
         <v>100</v>
       </c>
       <c r="BO18" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP18" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP18" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ18" s="37">
         <v>61</v>
@@ -5526,10 +5523,10 @@
         <v>0</v>
       </c>
       <c r="BT18" s="32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BU18" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BV18" s="32" t="s">
         <v>105</v>
@@ -5550,7 +5547,7 @@
         <v>96</v>
       </c>
       <c r="CB18" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CC18" s="37">
         <v>1</v>
@@ -5562,7 +5559,7 @@
       <c r="CF18" s="34"/>
       <c r="CG18" s="32"/>
       <c r="CH18" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:86" x14ac:dyDescent="0.3">
@@ -5582,10 +5579,10 @@
         <v>100014</v>
       </c>
       <c r="F19" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="G19" s="34" t="s">
         <v>267</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>268</v>
       </c>
       <c r="H19" s="34" t="s">
         <v>86</v>
@@ -5594,19 +5591,19 @@
         <v>87</v>
       </c>
       <c r="J19" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="K19" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="K19" s="34" t="s">
+      <c r="L19" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="L19" s="34" t="s">
+      <c r="M19" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="M19" s="32" t="s">
+      <c r="N19" s="32" t="s">
         <v>272</v>
-      </c>
-      <c r="N19" s="32" t="s">
-        <v>273</v>
       </c>
       <c r="O19" s="32" t="s">
         <v>93</v>
@@ -5621,7 +5618,7 @@
         <v>46112</v>
       </c>
       <c r="S19" s="33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T19" s="32"/>
       <c r="U19" s="32"/>
@@ -5629,31 +5626,31 @@
       <c r="W19" s="33"/>
       <c r="X19" s="36"/>
       <c r="Y19" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z19" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="AA19" s="34" t="s">
         <v>275</v>
-      </c>
-      <c r="AA19" s="34" t="s">
-        <v>276</v>
       </c>
       <c r="AB19" s="35">
         <v>41964</v>
       </c>
       <c r="AC19" s="33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AD19" s="35">
         <v>46121</v>
       </c>
       <c r="AE19" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF19" s="37">
         <v>3246163787</v>
       </c>
       <c r="AG19" s="34" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AH19" s="32" t="s">
         <v>98</v>
@@ -5700,7 +5697,7 @@
         <v>46112</v>
       </c>
       <c r="BH19" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BI19" s="35" t="s">
         <v>96</v>
@@ -5721,10 +5718,10 @@
         <v>100</v>
       </c>
       <c r="BO19" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP19" s="32" t="s">
         <v>163</v>
-      </c>
-      <c r="BP19" s="32" t="s">
-        <v>164</v>
       </c>
       <c r="BQ19" s="37">
         <v>61</v>
@@ -5736,7 +5733,7 @@
         <v>-7</v>
       </c>
       <c r="BT19" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BU19" s="32" t="s">
         <v>104</v>
@@ -5745,7 +5742,7 @@
         <v>105</v>
       </c>
       <c r="BW19" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BX19" s="35">
         <v>44267</v>
@@ -5760,7 +5757,7 @@
         <v>96</v>
       </c>
       <c r="CB19" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="CC19" s="37">
         <v>1</v>
@@ -5772,7 +5769,7 @@
       <c r="CF19" s="34"/>
       <c r="CG19" s="32"/>
       <c r="CH19" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:86" x14ac:dyDescent="0.3">
@@ -5792,10 +5789,10 @@
         <v>100014</v>
       </c>
       <c r="F20" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="G20" s="34" t="s">
         <v>279</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>280</v>
       </c>
       <c r="H20" s="34" t="s">
         <v>86</v>
@@ -5804,19 +5801,19 @@
         <v>87</v>
       </c>
       <c r="J20" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="K20" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="L20" s="34" t="s">
         <v>282</v>
       </c>
-      <c r="L20" s="34" t="s">
+      <c r="M20" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="N20" s="32" t="s">
         <v>284</v>
-      </c>
-      <c r="N20" s="32" t="s">
-        <v>285</v>
       </c>
       <c r="O20" s="32" t="s">
         <v>93</v>
@@ -5831,7 +5828,7 @@
         <v>46100</v>
       </c>
       <c r="S20" s="33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T20" s="32">
         <v>435945416</v>
@@ -5843,7 +5840,7 @@
         <v>46100</v>
       </c>
       <c r="W20" s="33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="X20" s="36"/>
       <c r="Y20" s="32" t="s">
@@ -5869,7 +5866,7 @@
       </c>
       <c r="AF20" s="37"/>
       <c r="AG20" s="34" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AH20" s="32" t="s">
         <v>98</v>
@@ -5937,10 +5934,10 @@
         <v>100</v>
       </c>
       <c r="BO20" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BP20" s="32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BQ20" s="37">
         <v>69</v>
@@ -5952,7 +5949,7 @@
         <v>-19</v>
       </c>
       <c r="BT20" s="32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BU20" s="32" t="s">
         <v>104</v>
@@ -5961,7 +5958,7 @@
         <v>105</v>
       </c>
       <c r="BW20" s="32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BX20" s="35">
         <v>44025</v>
@@ -5976,7 +5973,7 @@
         <v>96</v>
       </c>
       <c r="CB20" s="34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="CC20" s="37">
         <v>1</v>

--- a/PROGRAMACION 12-04-2026.xlsx
+++ b/PROGRAMACION 12-04-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prueba\ENVIO MASIVO DE MENSAJES 2026 MARZO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A7A8C0-A3B1-41CB-821C-7332DCB7331D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C6DC0D-1121-47EE-B31F-1BC84A9F962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B72AB2B8-5376-4A67-BE8D-5E91B2913CFD}"/>
   </bookViews>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="2" spans="1:86" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32">
-        <v>2644479</v>
+        <v>2644486</v>
       </c>
       <c r="B2" s="32">
-        <v>45485</v>
+        <v>45491</v>
       </c>
       <c r="C2" s="32">
         <v>71816720</v>
@@ -1602,7 +1602,7 @@
         <v>95</v>
       </c>
       <c r="AD2" s="35">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AE2" s="32" t="s">
         <v>97</v>
@@ -1733,10 +1733,10 @@
     </row>
     <row r="3" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
-        <v>2644480</v>
+        <v>2644487</v>
       </c>
       <c r="B3" s="32">
-        <v>45486</v>
+        <v>45492</v>
       </c>
       <c r="C3" s="32">
         <v>78664</v>
@@ -1818,7 +1818,7 @@
         <v>95</v>
       </c>
       <c r="AD3" s="35">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AE3" s="32" t="s">
         <v>97</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="4" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A4" s="32">
-        <v>2644481</v>
+        <v>2644488</v>
       </c>
       <c r="B4" s="32">
-        <v>45487</v>
+        <v>45493</v>
       </c>
       <c r="C4" s="32">
         <v>686614</v>
@@ -2036,7 +2036,7 @@
         <v>95</v>
       </c>
       <c r="AD4" s="35">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AE4" s="32" t="s">
         <v>129</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="5" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A5" s="32">
-        <v>2644482</v>
+        <v>2644489</v>
       </c>
       <c r="B5" s="32">
-        <v>45488</v>
+        <v>45494</v>
       </c>
       <c r="C5" s="32">
         <v>473283</v>
@@ -2254,7 +2254,7 @@
         <v>95</v>
       </c>
       <c r="AD5" s="35">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AE5" s="32" t="s">
         <v>129</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="6" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A6" s="32">
-        <v>2644483</v>
+        <v>2644490</v>
       </c>
       <c r="B6" s="32">
-        <v>45489</v>
+        <v>45495</v>
       </c>
       <c r="C6" s="32">
         <v>455571</v>
@@ -2462,7 +2462,7 @@
         <v>96</v>
       </c>
       <c r="AD6" s="35">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AE6" s="32" t="s">
         <v>97</v>
@@ -2593,10 +2593,10 @@
     </row>
     <row r="7" spans="1:86" x14ac:dyDescent="0.3">
       <c r="A7" s="32">
-        <v>2644484</v>
+        <v>2644491</v>
       </c>
       <c r="B7" s="32">
-        <v>45490</v>
+        <v>45496</v>
       </c>
       <c r="C7" s="32">
         <v>505024</v>
@@ -2678,7 +2678,7 @@
         <v>95</v>
       </c>
       <c r="AD7" s="35">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="AE7" s="32" t="s">
         <v>97</v>

--- a/PROGRAMACION 12-04-2026.xlsx
+++ b/PROGRAMACION 12-04-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prueba\ENVIO MASIVO DE MENSAJES 2026 MARZO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programacion 2026\certi-redes-operacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C6DC0D-1121-47EE-B31F-1BC84A9F962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87FCABA-D4F5-496A-BED6-4D271F132DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B72AB2B8-5376-4A67-BE8D-5E91B2913CFD}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B72AB2B8-5376-4A67-BE8D-5E91B2913CFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Coordinación" sheetId="1" r:id="rId1"/>
@@ -1246,16 +1246,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6872984D-384B-474A-8400-FCFD480CF102}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:CH7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="37.21875" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="37.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:86" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1515,12 +1515,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:86" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:86" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
-        <v>2644486</v>
+        <v>16</v>
       </c>
       <c r="B2" s="32">
-        <v>45491</v>
+        <v>10</v>
       </c>
       <c r="C2" s="32">
         <v>71816720</v>
@@ -1602,7 +1602,7 @@
         <v>95</v>
       </c>
       <c r="AD2" s="35">
-        <v>46141</v>
+        <v>46152</v>
       </c>
       <c r="AE2" s="32" t="s">
         <v>97</v>
@@ -1731,12 +1731,12 @@
       <c r="CG2" s="32"/>
       <c r="CH2" s="34"/>
     </row>
-    <row r="3" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
-        <v>2644487</v>
+        <v>17</v>
       </c>
       <c r="B3" s="32">
-        <v>45492</v>
+        <v>11</v>
       </c>
       <c r="C3" s="32">
         <v>78664</v>
@@ -1818,7 +1818,7 @@
         <v>95</v>
       </c>
       <c r="AD3" s="35">
-        <v>46141</v>
+        <v>46152</v>
       </c>
       <c r="AE3" s="32" t="s">
         <v>97</v>
@@ -1949,12 +1949,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
-        <v>2644488</v>
+        <v>18</v>
       </c>
       <c r="B4" s="32">
-        <v>45493</v>
+        <v>12</v>
       </c>
       <c r="C4" s="32">
         <v>686614</v>
@@ -2036,7 +2036,7 @@
         <v>95</v>
       </c>
       <c r="AD4" s="35">
-        <v>46141</v>
+        <v>46152</v>
       </c>
       <c r="AE4" s="32" t="s">
         <v>129</v>
@@ -2167,12 +2167,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
-        <v>2644489</v>
+        <v>19</v>
       </c>
       <c r="B5" s="32">
-        <v>45494</v>
+        <v>13</v>
       </c>
       <c r="C5" s="32">
         <v>473283</v>
@@ -2254,7 +2254,7 @@
         <v>95</v>
       </c>
       <c r="AD5" s="35">
-        <v>46141</v>
+        <v>46152</v>
       </c>
       <c r="AE5" s="32" t="s">
         <v>129</v>
@@ -2383,12 +2383,12 @@
       <c r="CG5" s="32"/>
       <c r="CH5" s="34"/>
     </row>
-    <row r="6" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
-        <v>2644490</v>
+        <v>20</v>
       </c>
       <c r="B6" s="32">
-        <v>45495</v>
+        <v>14</v>
       </c>
       <c r="C6" s="32">
         <v>455571</v>
@@ -2462,7 +2462,7 @@
         <v>96</v>
       </c>
       <c r="AD6" s="35">
-        <v>46141</v>
+        <v>46152</v>
       </c>
       <c r="AE6" s="32" t="s">
         <v>97</v>
@@ -2591,12 +2591,12 @@
       <c r="CG6" s="32"/>
       <c r="CH6" s="34"/>
     </row>
-    <row r="7" spans="1:86" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
-        <v>2644491</v>
+        <v>21</v>
       </c>
       <c r="B7" s="32">
-        <v>45496</v>
+        <v>15</v>
       </c>
       <c r="C7" s="32">
         <v>505024</v>
@@ -2678,7 +2678,7 @@
         <v>95</v>
       </c>
       <c r="AD7" s="35">
-        <v>46141</v>
+        <v>46152</v>
       </c>
       <c r="AE7" s="32" t="s">
         <v>97</v>

--- a/PROGRAMACION 12-04-2026.xlsx
+++ b/PROGRAMACION 12-04-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programacion 2026\certi-redes-operacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87FCABA-D4F5-496A-BED6-4D271F132DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD04BBFA-0C0B-4D62-9B85-985956879A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B72AB2B8-5376-4A67-BE8D-5E91B2913CFD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B72AB2B8-5376-4A67-BE8D-5E91B2913CFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Coordinación" sheetId="1" r:id="rId1"/>
@@ -537,7 +537,7 @@
     <t>E1</t>
   </si>
   <si>
-    <t>Prueba Mensaje</t>
+    <t>FERNANDO TORO RIOS</t>
   </si>
 </sst>
 </file>
